--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.7870640289788</v>
+        <v>4.515397904709056</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99620355335745</v>
+        <v>4.711883077420585</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97629551641782</v>
+        <v>2.758648021417896</v>
       </c>
       <c r="F2" t="n">
-        <v>22.10566865689325</v>
+        <v>3.592171156745154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.16569109749539</v>
+        <v>9.939424803343002</v>
       </c>
       <c r="D3" t="n">
-        <v>57.91719457679077</v>
+        <v>9.4115441187285</v>
       </c>
       <c r="E3" t="n">
-        <v>16.97629551641782</v>
+        <v>2.758648021417896</v>
       </c>
       <c r="F3" t="n">
-        <v>22.10566865689325</v>
+        <v>3.592171156745154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.10677720118998</v>
+        <v>9.604851295193372</v>
       </c>
       <c r="D4" t="n">
-        <v>71.12404595312918</v>
+        <v>11.55765746738349</v>
       </c>
       <c r="E4" t="n">
-        <v>16.97629551641782</v>
+        <v>2.758648021417896</v>
       </c>
       <c r="F4" t="n">
-        <v>22.10566865689325</v>
+        <v>3.592171156745154</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.5884958365766</v>
+        <v>10.8206305734437</v>
       </c>
       <c r="D5" t="n">
-        <v>81.01325177220485</v>
+        <v>13.16465341298329</v>
       </c>
       <c r="E5" t="n">
-        <v>16.97629551641782</v>
+        <v>2.758648021417896</v>
       </c>
       <c r="F5" t="n">
-        <v>22.10566865689325</v>
+        <v>3.592171156745154</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>79.11823079698158</v>
+        <v>12.85671250450951</v>
       </c>
       <c r="D6" t="n">
-        <v>93.53865669358302</v>
+        <v>15.20003171270724</v>
       </c>
       <c r="E6" t="n">
-        <v>16.97629551641782</v>
+        <v>2.758648021417896</v>
       </c>
       <c r="F6" t="n">
-        <v>22.10566865689325</v>
+        <v>3.592171156745154</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
